--- a/authoring/17108A-5-120_診斷資料.xlsx
+++ b/authoring/17108A-5-120_診斷資料.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="異常資訊" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="確認資訊" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="判斷節點" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="機型" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="異常資訊" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="確認資訊" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="判斷節點" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,62 +429,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="47" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fault_ID</t>
+          <t>Model_ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>名稱</t>
+          <t>型號名稱</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>關鍵字</t>
+          <t>系列</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>類別</t>
+          <t>圖片</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>優先等級</t>
+          <t>是否已建置</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>是否已建置</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>起始節點</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>手冊章節</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
@@ -492,399 +475,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F_CALI</t>
+          <t>17108A-5-120</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Calibration Error 校正值異常</t>
+          <t>17108A-5-120 電池化成測試器</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>校正值異常,Slope,Calibration Out of Range</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>校正</t>
+          <t>images/17108A-5-120.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>是</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4.8節</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>校正值 Slope&gt;20%，判定為 Calibration Out of Range。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>F_OCP</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>OCP／OVP 過電流過電壓保護</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OCP,OVP,過電流,過電壓,Input Voltage Protection</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>保護</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>OCP_1</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>4.1節</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Iout&gt;134A 或 Vout&gt;5.8V 或 Vin&gt;14V 時觸發。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>F_OTP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>OTP 單機環溫過溫保護</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OTP,過溫,溫度異常</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>溫度</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>4.2節</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>單機環溫 &gt;100°C 觸發過溫保護。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>F_CONTACT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>接觸錯誤／感應異常保護</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>接觸錯誤,感應異常,Vmi,Vmo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>量測</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4.3節</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ABS(Vmi-Vmo)/I 超出設定值，Sense/Drive 線路或量測電路異常。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>F_FAN</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FAN 風扇異常保護</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Fan,風扇,異常,鎖轉,轉速</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>散熱</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>FAN_1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4.5節</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>風扇電源異常或風扇本體損壞造成 Fan Lock 保護。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>F_NET</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>網路通訊異常</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>網路,LAN,IP,通訊異常</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>通訊</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.4節</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>PC 與單機之間 LAN 通訊異常，無法連線。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>F_SYSCFG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>System Config Error</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>System Config,模組錯誤,12V,13V</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>控制</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>4.6節</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>前級轉換器(AC-DC)異常或通道數/Slot數設定錯誤。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>F_ADC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ADC Error 讀值異常</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ADC,讀值異常,固定0V,固定0A</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>量測</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>4.7節</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>電壓/電流讀值固定不跳動，疑似 ADC 或 A 板異常。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>F_NOOUTPUT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>無輸出電壓，DVM無讀值</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>無輸出電壓,DVM無讀值,CV4V 0V 0V</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>校驗證查修</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NOV_1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>5.2.1節</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>執行 8000 程式校驗證時，設定電壓後完全無輸出，內部讀值與 DVM 實測值皆為 0V。</t>
+          <t>電池化成測試器，120A 一體機。</t>
         </is>
       </c>
     </row>
@@ -894,6 +510,528 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="47" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fault_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>關鍵字</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>優先等級</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>是否已建置</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>起始節點</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>手冊章節</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>F_CALI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>17108A-5-120</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Calibration Error 校正值異常</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>校正值異常,Slope,Calibration Out of Range</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>校正</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4.8節</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>校正值 Slope&gt;20%，判定為 Calibration Out of Range。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F_OCP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>17108A-5-120</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OCP／OVP 過電流過電壓保護</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OCP,OVP,過電流,過電壓,Input Voltage Protection</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>保護</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OCP_1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4.1節</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Iout&gt;134A 或 Vout&gt;5.8V 或 Vin&gt;14V 時觸發。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F_OTP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>17108A-5-120</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OTP 單機環溫過溫保護</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OTP,過溫,溫度異常</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4.2節</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>單機環溫 &gt;100°C 觸發過溫保護。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F_CONTACT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>17108A-5-120</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>接觸錯誤／感應異常保護</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>接觸錯誤,感應異常,Vmi,Vmo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>量測</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4.3節</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ABS(Vmi-Vmo)/I 超出設定值，Sense/Drive 線路或量測電路異常。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F_FAN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>17108A-5-120</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FAN 風扇異常保護</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fan,風扇,異常,鎖轉,轉速</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>散熱</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FAN_1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4.5節</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>風扇電源異常或風扇本體損壞造成 Fan Lock 保護。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F_NET</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17108A-5-120</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>網路通訊異常</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>網路,LAN,IP,通訊異常</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>通訊</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4.4節</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PC 與單機之間 LAN 通訊異常，無法連線。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F_SYSCFG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>17108A-5-120</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>System Config Error</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>System Config,模組錯誤,12V,13V</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>控制</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4.6節</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>前級轉換器(AC-DC)異常或通道數/Slot數設定錯誤。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F_ADC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>17108A-5-120</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ADC Error 讀值異常</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ADC,讀值異常,固定0V,固定0A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>量測</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4.7節</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>電壓/電流讀值固定不跳動，疑似 ADC 或 A 板異常。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F_NOOUTPUT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>17108A-5-120</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>無輸出電壓，DVM無讀值</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>無輸出電壓,DVM無讀值,CV4V 0V 0V</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>校驗證查修</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NOV_1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5.2.1節</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>執行 8000 程式校驗證時，設定電壓後完全無輸出，內部讀值與 DVM 實測值皆為 0V。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1747,7 +1885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/authoring/17108A-5-120_診斷資料.xlsx
+++ b/authoring/17108A-5-120_診斷資料.xlsx
@@ -618,7 +618,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>4.8節</t>
@@ -718,7 +717,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>4.2節</t>
@@ -766,7 +764,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>4.3節</t>
@@ -866,7 +863,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>4.4節</t>
@@ -914,7 +910,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>4.6節</t>
@@ -962,7 +957,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>4.7節</t>
@@ -1037,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1083,27 +1077,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C_OCP_PERIPH</t>
+          <t>C_OCP_R603R605</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OCP/OVP/Input_OVP/比較器/Ref voltage 週邊元件</t>
+          <t>R603 / R605</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>使用三用電錶量測 R726/R868、R724/R866、C710/C850、R744/R888、R745/R887、C708/C848 等週邊電阻電容</t>
+          <t>量測 R603 右邊電壓、R605 右邊電壓</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R726/R868=75KΩ±1%; R724/R866=100KΩ±1%; C710/C850=0.1uF±10%; R744/R888=10KΩ±1%; R745/R887=10KΩ±1%; C708/C848=1uF±10%</t>
+          <t>R603右邊應為10V；R605右邊應為5V</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ω/uF</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1115,22 +1109,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C_OCP_U602</t>
+          <t>C_OCP_DGROUP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U602 Pin5~Pin7</t>
+          <t>D602 / D607 / D608 (input_OCP_bar / Fault_02)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>以 DMM 量測 U602 Pin5、Pin6、Pin7 電壓</t>
+          <t>以 DMM 量測二極體兩端電壓</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>正常: Pin6=3.33V,Pin5=2.5V,Pin7=0V；OCP觸發: Pin6≈0.7V,Pin5=2.5V,Pin7=3.33V</t>
+          <t>正常應為 HIGH；電壓 &lt;1V 視為 LOW(異常)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1147,118 +1141,118 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C_OCP_R603R605</t>
+          <t>C_FAN_DEBRIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R603 / R605</t>
+          <t>風扇葉片/入風口</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>量測 R603 右邊電壓、R605 右邊電壓</t>
+          <t>目視+手動檢查是否有異物、積塵造成堵轉</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>R603右邊應為10V；R605右邊應為5V</t>
+          <t>無異物、無堵轉</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>散熱</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C_OCP_DGROUP</t>
+          <t>C_FAN_BODY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D602 / D607 / D608 (input_OCP_bar / Fault_02)</t>
+          <t>風扇本體</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>以 DMM 量測二極體兩端電壓</t>
+          <t>通電測試風扇是否正常運轉(有無異音、轉速是否明顯不足)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>正常應為 HIGH；電壓 &lt;1V 視為 LOW(異常)</t>
+          <t>運轉順暢、無異音</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>散熱</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C_OCP_INPUTOVP</t>
+          <t>C_FAN_POWER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U602 Pin1 對 Pin4(GND) / R620</t>
+          <t>風扇線材(FT板) / 風扇電源(S板→FT板)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>量測 U602 Pin1 對 GND 電壓；量測 R620 阻抗</t>
+          <t>量測風扇電源迴路電壓</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pin1為HIGH代表Input OVP；R620應為15KΩ±0.1%</t>
+          <t>供電正常，無斷路或電壓異常</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>V/Ω</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>散熱</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C_OCP_R816</t>
+          <t>C_NOV_MOSRELAY_V</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R816 下方 / R791 下方</t>
+          <t>MOS Relay 前端</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>量測 R816(或R791) 下方電壓</t>
+          <t>量測 MOS Relay 前端是否有電壓</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>正常應為 HIGH，LOW 代表控制IC(8450)跳OCP/OV</t>
+          <t>依機種規格應有電壓</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1268,29 +1262,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>功率</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C_OCP_C849C850</t>
+          <t>C_NOV_GS_V</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C849(OVP) / C850(OCP) / C709(OVP) / C710(OCP)</t>
+          <t>MOS Relay G-S 腳</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>量測電容電壓</t>
+          <t>量測 MOS Relay Gate-Source 電壓</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>電壓 &gt;1.25V 代表該相觸發對應保護</t>
+          <t>依驅動規格，正常應能驅動導通</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1300,29 +1294,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>功率</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C_OCP_VDROP</t>
+          <t>C_NOV_U101U102</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R890/R891 下方壓差 / R747/R748 下方壓差</t>
+          <t>U101 &amp; U102 PIN1 / PIN3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>量測電阻下方壓差</t>
+          <t>量測驅動 IC 輸入輸出電壓</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>應等於電池電壓</t>
+          <t>依機種規格</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1332,29 +1326,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>功率</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C_FAN_DEBRIS</t>
+          <t>C_NOV_GS_PWM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>風扇葉片/入風口</t>
+          <t>MOS G-S 腳</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>目視+手動檢查是否有異物、積塵造成堵轉</t>
+          <t>以示波器量測 MOS Gate-Source 是否有 PWM 波形</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>無異物、無堵轉</t>
+          <t>應有連續 PWM 波形</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1364,29 +1358,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>散熱</t>
+          <t>功率</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C_FAN_BODY</t>
+          <t>C_NOV_U708803_1510</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>風扇本體</t>
+          <t>U708/U803 PIN15 &amp; PIN10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>通電測試風扇是否正常運轉(有無異音、轉速是否明顯不足)</t>
+          <t>示波器量測 PWM 波形</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>運轉順暢、無異音</t>
+          <t>應有 PWM 波形</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1396,66 +1390,66 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>散熱</t>
+          <t>功率</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C_FAN_POWER</t>
+          <t>C_NOV_U708803_1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>風扇線材(FT板) / 風扇電源(S板→FT板)</t>
+          <t>U708/U803 PIN1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>量測風扇電源迴路電壓</t>
+          <t>示波器量測 PWM 波形</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>供電正常，無斷路或電壓異常</t>
+          <t>應有 PWM 波形</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>散熱</t>
+          <t>功率</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C_NOV_MOSRELAY_V</t>
+          <t>C_NOV_U707802_6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MOS Relay 前端</t>
+          <t>U707/U802 PIN6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>量測 MOS Relay 前端是否有電壓</t>
+          <t>示波器量測波形</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>依機種規格應有電壓</t>
+          <t>應有波形</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1467,27 +1461,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C_NOV_GS_V</t>
+          <t>C_NOV_U707802_5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MOS Relay G-S 腳</t>
+          <t>U707/U802 PIN5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>量測 MOS Relay Gate-Source 電壓</t>
+          <t>示波器量測波形</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>依驅動規格，正常應能驅動導通</t>
+          <t>應有波形</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1499,27 +1493,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C_NOV_U101U102</t>
+          <t>C_NOV_U706801_2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U101 &amp; U102 PIN1 / PIN3</t>
+          <t>U706/U801 PIN2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>量測驅動 IC 輸入輸出電壓</t>
+          <t>示波器量測波形</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>依機種規格</t>
+          <t>應有波形</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1531,27 +1525,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C_NOV_GS_PWM</t>
+          <t>C_NOV_U706801_5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MOS G-S 腳</t>
+          <t>U706/U801 PIN5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>以示波器量測 MOS Gate-Source 是否有 PWM 波形</t>
+          <t>DMM量測電壓</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>應有連續 PWM 波形</t>
+          <t>應為 5V</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1563,27 +1557,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C_NOV_U708803_1510</t>
+          <t>C_NOV_PIN9GROUP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U708/U803 PIN15 &amp; PIN10</t>
+          <t>PIN9 / D703&amp;D803負端 / U705&amp;U804 G腳</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>示波器量測 PWM 波形</t>
+          <t>DMM量測各點電壓</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>應有 PWM 波形</t>
+          <t>U705/U804 G腳應為 5V</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1595,27 +1589,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C_NOV_U708803_1</t>
+          <t>C_NOV_U702805_PINS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U708/U803 PIN1</t>
+          <t>U702/U805 PIN39/40/44/49/60、C766</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>示波器量測 PWM 波形</t>
+          <t>DMM量測各腳位電壓</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>應有 PWM 波形</t>
+          <t>依機種規格，各點電壓應正常</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1627,86 +1621,86 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C_NOV_U707802_6</t>
+          <t>C_NOV_U1001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U707/U802 PIN6</t>
+          <t>U1001 PIN1 / R1007</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>示波器量測波形</t>
+          <t>DMM量測電壓</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>應有波形</t>
+          <t>依機種規格應正常</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>數位</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C_NOV_U707802_5</t>
+          <t>C_NOV_U322GROUP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U707/U802 PIN5</t>
+          <t>U306 / U307 / U312</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>示波器量測波形</t>
+          <t>DMM量測各IC電壓</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>應有波形</t>
+          <t>依機種規格應正常</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>數位</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C_NOV_U706801_2</t>
+          <t>C_OCP_RESTART</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U706/U801 PIN2</t>
+          <t>電源重開機(小軟體)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>示波器量測波形</t>
+          <t>重新開關電源，使用小軟體確認機台是否恢復正常</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>應有波形</t>
+          <t>無異常</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1716,167 +1710,231 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>保護</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C_NOV_U706801_5</t>
+          <t>C_OCP_R726R868</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U706/U801 PIN5</t>
+          <t>R726 / R868</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DMM量測電壓</t>
+          <t>使用三用電錶量測 R726、R868 阻值</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>應為 5V</t>
+          <t>75KΩ±1%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Ω</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>保護</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C_NOV_PIN9GROUP</t>
+          <t>C_OCP_R724R866</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PIN9 / D703&amp;D803負端 / U705&amp;U804 G腳</t>
+          <t>R724 / R866</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DMM量測各點電壓</t>
+          <t>使用三用電錶量測 R724、R866 阻值</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>U705/U804 G腳應為 5V</t>
+          <t>100KΩ±1%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Ω</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>保護</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C_NOV_U702805_PINS</t>
+          <t>C_OCP_C710C850</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U702/U805 PIN39/40/44/49/60、C766</t>
+          <t>C710 / C850</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DMM量測各腳位電壓</t>
+          <t>使用三用電錶量測 C710、C850 容值</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>依機種規格，各點電壓應正常</t>
+          <t>0.1uF±10%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>uF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>保護</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C_NOV_U1001</t>
+          <t>C_OCP_R744R888</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U1001 PIN1 / R1007</t>
+          <t>R744 / R888</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DMM量測電壓</t>
+          <t>使用三用電錶量測 R744、R888 阻值</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>依機種規格應正常</t>
+          <t>10KΩ±1%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Ω</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>數位</t>
+          <t>保護</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C_NOV_U322GROUP</t>
+          <t>C_OCP_R745R887</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U306 / U307 / U312</t>
+          <t>R745 / R887</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DMM量測各IC電壓</t>
+          <t>使用三用電錶量測 R745、R887 阻值</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>依機種規格應正常</t>
+          <t>10KΩ±1%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Ω</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>數位</t>
+          <t>保護</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C_OCP_C708C848</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C708 / C848</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>使用三用電錶量測 C708、C848 容值</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1uF±10%</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>uF</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>保護</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C_OCP_LAYOUT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>R603/R605 週邊 PCB layout</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>以電錶輔助跳線：10V 點跳線到 C611 上方；5V 點跳線到 R619 下方；Pin5 跳線到 C540</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>跳線後功能恢復正常視為 layout 斷路</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>保護</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1961,499 +2019,469 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OCP_1</t>
+          <t>FAN_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F_OCP</t>
+          <t>F_FAN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_OCP_PERIPH</t>
+          <t>C_FAN_DEBRIS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>如尚未啟動電源即出現 OCP，先量測 OCP/OVP/Input_OVP/比較器/Ref voltage 週邊元件，確認是否都在合格範圍內。</t>
+          <t>檢查風扇是否有異物或積塵造成堵轉。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>有元件數值超出合格範圍</t>
+          <t>有異物/堵轉</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>END::更換超出公差的週邊元件（對照規格表）::依規格表更換異常的電阻/電容</t>
+          <t>END::風扇堵轉::清除異物/積塵後重新測試</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>全部元件數值正常</t>
+          <t>無異物，風扇順暢</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>OCP_2</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>FAN_2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OCP_2</t>
+          <t>FAN_2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F_OCP</t>
+          <t>F_FAN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_OCP_U602</t>
+          <t>C_FAN_BODY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>量測 U602 Pin5~Pin7 電壓。正常：Pin6=3.33V、Pin5=2.5V、Pin7=0V；OCP觸發時：Pin6≈0.7V、Pin5=2.5V、Pin7=3.33V。量測結果符合上述哪一種？</t>
+          <t>確認無堵轉後，通電檢查風扇本體是否損壞（完全不轉/有異音/轉速明顯不足）。</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>符合正常或OCP觸發任一種模式</t>
+          <t>風扇本體損壞</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>OCP_4</t>
+          <t>END::風扇本體損壞::更換風扇</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>都不符合(讀值異常/中間值)</t>
+          <t>風扇本體正常</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>OCP_3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>FAN_3</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OCP_3</t>
+          <t>FAN_3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F_OCP</t>
+          <t>F_FAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_OCP_R603R605</t>
+          <t>C_FAN_POWER</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>量 R603 右邊是否為10V；R605 右邊是否為5V。</t>
+          <t>檢查風扇電源迴路（S板→FT板→風扇）是否正常供電。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>皆正常(10V/5V)</t>
+          <t>電源異常</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>END::邏輯IC(LM393)異常，造成Pin1輸出異常::更換 LM393</t>
+          <t>END::S板電源異常導致風扇無法正常運轉::更換S板後重新開機確認異常是否解除；若未解除，接續排查FT板</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>任一不正常</t>
+          <t>電源正常</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>END::PCB layout斷路::依手冊跳線：10V點跳線到C611上方、5V點跳線到R619(下)、Pin5跳線到C540</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>END::風扇本體與線路皆正常，但面板仍顯示異常::判斷為FT板電路異常，更換FT板後開機確認</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OCP_4</t>
+          <t>NOV_1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F_OCP</t>
+          <t>F_NOOUTPUT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C_OCP_DGROUP</t>
+          <t>C_NOV_MOSRELAY_V</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>量測 D602、D607、D608(input_OCP_bar / Fault_02)。正常應為HIGH，&lt;1V視為LOW(異常)。D608對應Input OVP路徑，D602/D607對應OCP/OVP路徑。</t>
+          <t>不良現象：無輸出電壓，DVM無讀值。查修方向：確認 MOS Relay 前是否有電壓。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>D608 為 LOW</t>
+          <t>有電壓(猜測MOS Relay未導通)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OCP_5</t>
+          <t>NOV_1B</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>D602 或 D607 為 LOW</t>
+          <t>無電壓</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>OCP_6</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>皆為 HIGH(正常)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>END::保護迴路偵測本身正常，異常另有原因::建議會同資深工程師覆核控制IC與命令路徑，必要時更換數位板</t>
+          <t>NOV_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OCP_5</t>
+          <t>NOV_1B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F_OCP</t>
+          <t>F_NOOUTPUT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C_OCP_INPUTOVP</t>
+          <t>C_NOV_GS_V</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>D608為LOW，代表可能跳 Input OVP。請先回想：OCP是否只在『放電』時才觸發？並量測 U602 Pin1 對 Pin4(GND) 是否為HIGH，以及 R620 阻抗是否為18KΩ。</t>
+          <t>確認 MOS Relay_GS 腳電壓是否正常。</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>放電時才觸發 且 Pin1為HIGH</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>END::確認為 Input OVP::檢查R620是否18KΩ±0.1%，阻抗異常則更換R620；阻抗正常則為Input OVP偵測電路其他元件異常，需逐一排查</t>
+          <t>END::MOS Relay 零件損壞::更換 MOS Relay</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>非上述情況</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>END::非典型Input OVP案例::建議會同資深工程師覆核電路，勿逕自更換零件</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>END::驅動電路(U101/U102)異常::確認 U101/U102 PIN1、PIN3 是否有電壓，異常則更換相關驅動零件</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OCP_6</t>
+          <t>NOV_2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F_OCP</t>
+          <t>F_NOOUTPUT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C_OCP_R816</t>
+          <t>C_NOV_GS_PWM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D602或D607為LOW，量測 R816下(或R791下) 是否同為LOW。</t>
+          <t>MOS Relay前無電壓。確認 MOS_GS 腳是否有 PWM 波形。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>R816(或R791)下方為LOW</t>
+          <t>有 PWM 波形</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OCP_7</t>
+          <t>END::MOS 可能損壞::更換 MOS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>為HIGH(不同)</t>
+          <t>無 PWM 波形</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>END::控制IC(8450)未跳保護::建議另尋訊號路徑異常點，可能為量測電路本身異常</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>NOV_3A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OCP_7</t>
+          <t>NOV_3A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F_OCP</t>
+          <t>F_NOOUTPUT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C_OCP_C849C850</t>
+          <t>C_NOV_U708803_1510</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>R816(或R791)為LOW，代表控制IC 8450 跳 OCP/OV。量測 C849(OVP)/C850(OCP)（或另一相 C709(OVP)/C710(OCP)）電壓是否超過1.25V。</t>
+          <t>確認 U708/U803 PIN15 與 PIN10 是否有 PWM 波形。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C849(或C709) 超過1.25V (OVP)</t>
+          <t>有波形</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OCP_8</t>
+          <t>END::確認MOS背面(功率級)零件是否異常::進一步量測MOS周邊被動元件，異常則更換</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C850(或C710) 超過1.25V (OCP)</t>
+          <t>無波形</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>END::該相觸發 OCP 過電流保護::檢查功率級電流迴路與MOSFET/電流取樣電路，比對更換相關功率元件</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>NOV_3B</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OCP_8</t>
+          <t>NOV_3B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>F_OCP</t>
+          <t>F_NOOUTPUT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C_OCP_VDROP</t>
+          <t>C_NOV_U708803_1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>確認為OVP，需量測實際觸發電壓：C849超過1.25V則量R890與R891下方壓差；C709超過1.25V則量R747與R748下方壓差，此壓差應等於電池電壓。</t>
+          <t>確認 U708/U803 PIN1 是否有 PWM 波形。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>壓差 = 電池電壓(符合預期)</t>
+          <t>有波形</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>END::該相觸發 OVP 過電壓保護，屬正常保護動作::請確認電池/測試條件是否超出設備輸出電壓上限(5.8V)，非硬體故障</t>
+          <t>END::U708/U803本身可能異常::比對各腳位電壓及波形，異常則更換 U708/U803</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>壓差明顯異常(不等於電池電壓)</t>
+          <t>無波形</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>END::電壓量測迴路(Vmo)異常::更換 U702/U805 或相關量測迴路元件</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>NOV_4A</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FAN_1</t>
+          <t>NOV_4A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>F_FAN</t>
+          <t>F_NOOUTPUT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C_FAN_DEBRIS</t>
+          <t>C_NOV_U707802_6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>檢查風扇是否有異物或積塵造成堵轉。</t>
+          <t>往 U707/U802 查修：確認 PIN6 是否有波形。</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>有異物/堵轉</t>
+          <t>有波形</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>END::風扇堵轉::清除異物/積塵後重新測試</t>
+          <t>END::R757、R824 電阻可能異常::量測後異常則更換</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>無異物，風扇順暢</t>
+          <t>無波形</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FAN_2</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>NOV_4B</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FAN_2</t>
+          <t>NOV_4B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F_FAN</t>
+          <t>F_NOOUTPUT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C_FAN_BODY</t>
+          <t>C_NOV_U707802_5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>確認無堵轉後，通電檢查風扇本體是否損壞（完全不轉/有異音/轉速明顯不足）。</t>
+          <t>確認 U707/U802 PIN5 是否有波形。</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>風扇本體損壞</t>
+          <t>有波形</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>END::風扇本體損壞::更換風扇</t>
+          <t>END::附近零件或U707/U802本身可能異常::比對各腳位電壓與波形，異常則更換相關零件</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>風扇本體正常</t>
+          <t>無波形</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FAN_3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>NOV_5A</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FAN_3</t>
+          <t>NOV_5A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F_FAN</t>
+          <t>F_NOOUTPUT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C_FAN_POWER</t>
+          <t>C_NOV_U706801_2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>檢查風扇電源迴路（S板→FT板→風扇）是否正常供電。</t>
+          <t>往 U706/U801 查修：確認 PIN2 是否有波形。</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>電源異常</t>
+          <t>有波形</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>END::S板電源異常導致風扇無法正常運轉::更換S板後重新開機確認異常是否解除；若未解除，接續排查FT板</t>
+          <t>END::量測 U706_PIN2 與 U707_PIN5 是否導通::不導通表示PIN2到PIN5路徑斷路，需檢修該連接</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>電源正常</t>
+          <t>無波形</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>END::風扇本體與線路皆正常，但面板仍顯示異常::判斷為FT板電路異常，更換FT板後開機確認</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>NOV_5B</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NOV_1</t>
+          <t>NOV_5B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2463,41 +2491,39 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C_NOV_MOSRELAY_V</t>
+          <t>C_NOV_U706801_5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>不良現象：無輸出電壓，DVM無讀值。查修方向：確認 MOS Relay 前是否有電壓。</t>
+          <t>確認 U706/U801 PIN5 是否有5V。</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>有電壓(猜測MOS Relay未導通)</t>
+          <t>無5V</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NOV_1B</t>
+          <t>END::供電異常::往 U315/U314 查修，確認輸出是否正常，異常則更換</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>無電壓</t>
+          <t>有5V(正常)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NOV_2</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>NOV_5C</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NOV_1B</t>
+          <t>NOV_5C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2507,41 +2533,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C_NOV_GS_V</t>
+          <t>C_NOV_PIN9GROUP</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>確認 MOS Relay_GS 腳電壓是否正常。</t>
+          <t>比對 PIN9 電壓(決定輸出電壓大小)、確認 D703/D803 負端電壓、確認 U705/U804 G腳電壓是否為5V。</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>G腳電壓非5V</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>END::MOS Relay 零件損壞::更換 MOS Relay</t>
+          <t>END::供電或訊號路徑異常::往 U316 查修，並同時檢查 U702/U805，異常則更換</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>G腳電壓為5V(正常)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>END::驅動電路(U101/U102)異常::確認 U101/U102 PIN1、PIN3 是否有電壓，異常則更換相關驅動零件</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>NOV_6</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NOV_2</t>
+          <t>NOV_6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2551,41 +2575,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C_NOV_GS_PWM</t>
+          <t>C_NOV_U702805_PINS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MOS Relay前無電壓。確認 MOS_GS 腳是否有 PWM 波形。</t>
+          <t>往 U702/U805 查修：確認 PIN39、PIN40、PIN44、PIN49、PIN60 電壓，以及 C766 電壓是否正常。</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>有 PWM 波形</t>
+          <t>有任一電壓異常</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>END::MOS 可能損壞::更換 MOS</t>
+          <t>NOV_7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>無 PWM 波形</t>
+          <t>電壓皆正常</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NOV_3A</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>END::U702/U805本身工作正常但仍無輸出::進一步比對驅動時序，或將 U702/U805 整體模組送修</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NOV_3A</t>
+          <t>NOV_7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2595,41 +2617,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C_NOV_U708803_1510</t>
+          <t>C_NOV_U1001</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>確認 U708/U803 PIN15 與 PIN10 是否有 PWM 波形。</t>
+          <t>往 U1001 查修：確認 PIN1 電壓與 R1007 電壓是否正常。</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>有波形</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>END::確認MOS背面(功率級)零件是否異常::進一步量測MOS周邊被動元件，異常則更換</t>
+          <t>END::U1001周邊電路異常::往 U301 查修，確認各腳位電壓、波形，異常則更換U301</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>無波形</t>
+          <t>皆正常</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NOV_3B</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>NOV_8</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NOV_3B</t>
+          <t>NOV_8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2639,388 +2659,454 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C_NOV_U708803_1</t>
+          <t>C_NOV_U322GROUP</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>確認 U708/U803 PIN1 是否有 PWM 波形。</t>
+          <t>往 U322 查修：確認 U306、U307、U312 電壓是否正常。</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>有波形</t>
+          <t>有異常</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>END::U708/U803本身可能異常::比對各腳位電壓及波形，異常則更換 U708/U803</t>
+          <t>END::U306/U307/U312其中之一異常::更換異常的該顆IC</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>無波形</t>
+          <t>皆無異常</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NOV_4A</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>END::往 U319/U320/U321 查修::進一步比對，異常則更換 U319、U320 或 U321</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NOV_4A</t>
+          <t>OCP_1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>F_NOOUTPUT</t>
+          <t>F_OCP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C_NOV_U707802_6</t>
+          <t>C_OCP_RESTART</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>往 U707/U802 查修：確認 PIN6 是否有波形。</t>
+          <t>1. 重新開關電，並使用小軟體確認是否恢復正常。</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>有波形</t>
+          <t>是 [PASS]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>END::R757、R824 電阻可能異常::量測後異常則更換</t>
+          <t>END::解決::重新進行其它功能測試</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>無波形</t>
+          <t>否 [FAIL]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NOV_4B</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>OCP_2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NOV_4B</t>
+          <t>OCP_2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>F_NOOUTPUT</t>
+          <t>F_OCP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C_NOV_U707802_5</t>
+          <t>C_OCP_R726R868</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>確認 U707/U802 PIN5 是否有波形。</t>
+          <t>2. 量測 R726 與 R868，確認是否符合 75KΩ ±1%。</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>有波形</t>
+          <t>否 [FAIL]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>END::附近零件或U707/U802本身可能異常::比對各腳位電壓與波形，異常則更換相關零件</t>
+          <t>END::R726/R868 阻值異常::更換 R726/R868 後進行其它功能測試</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>無波形</t>
+          <t>是 [PASS]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NOV_5A</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>OCP_3</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NOV_5A</t>
+          <t>OCP_3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>F_NOOUTPUT</t>
+          <t>F_OCP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C_NOV_U706801_2</t>
+          <t>C_OCP_R724R866</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>往 U706/U801 查修：確認 PIN2 是否有波形。</t>
+          <t>3. 量測 R724 與 R866，確認是否符合 100KΩ ±1%。</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>有波形</t>
+          <t>否 [FAIL]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>END::量測 U706_PIN2 與 U707_PIN5 是否導通::不導通表示PIN2到PIN5路徑斷路，需檢修該連接</t>
+          <t>END::R724/R866 阻值異常::更換 R724/R866 後進行其它功能測試</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>無波形</t>
+          <t>是 [PASS]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NOV_5B</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>OCP_4</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NOV_5B</t>
+          <t>OCP_4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>F_NOOUTPUT</t>
+          <t>F_OCP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C_NOV_U706801_5</t>
+          <t>C_OCP_C710C850</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>確認 U706/U801 PIN5 是否有5V。</t>
+          <t>4. 量測 C710 與 C850，確認是否符合 0.1uF ±10%。</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>無5V</t>
+          <t>否 [FAIL]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>END::供電異常::往 U315/U314 查修，確認輸出是否正常，異常則更換</t>
+          <t>END::C710/C850 容值異常::更換 C710/C850 後進行其它功能測試</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>有5V(正常)</t>
+          <t>是 [PASS]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NOV_5C</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>OCP_5</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NOV_5C</t>
+          <t>OCP_5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>F_NOOUTPUT</t>
+          <t>F_OCP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C_NOV_PIN9GROUP</t>
+          <t>C_OCP_R744R888</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>比對 PIN9 電壓(決定輸出電壓大小)、確認 D703/D803 負端電壓、確認 U705/U804 G腳電壓是否為5V。</t>
+          <t>5. 量測 R744 與 R888，確認是否符合 10KΩ ±1%。</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>G腳電壓非5V</t>
+          <t>否 [FAIL]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>END::供電或訊號路徑異常::往 U316 查修，並同時檢查 U702/U805，異常則更換</t>
+          <t>END::R744/R888 阻值異常::更換 R744/R888 後進行其它功能測試</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>G腳電壓為5V(正常)</t>
+          <t>是 [PASS]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NOV_6</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>OCP_6</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NOV_6</t>
+          <t>OCP_6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>F_NOOUTPUT</t>
+          <t>F_OCP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>C_NOV_U702805_PINS</t>
+          <t>C_OCP_R745R887</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>往 U702/U805 查修：確認 PIN39、PIN40、PIN44、PIN49、PIN60 電壓，以及 C766 電壓是否正常。</t>
+          <t>6. 量測 R745 與 R887，確認是否符合 10KΩ ±1%。</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>有任一電壓異常</t>
+          <t>否 [FAIL]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NOV_7</t>
+          <t>END::R745/R887 阻值異常::更換 R745/R887 後進行其它功能測試</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>電壓皆正常</t>
+          <t>是 [PASS]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>END::U702/U805本身工作正常但仍無輸出::進一步比對驅動時序，或將 U702/U805 整體模組送修</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>OCP_7</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NOV_7</t>
+          <t>OCP_7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>F_NOOUTPUT</t>
+          <t>F_OCP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>C_NOV_U1001</t>
+          <t>C_OCP_C708C848</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>往 U1001 查修：確認 PIN1 電壓與 R1007 電壓是否正常。</t>
+          <t>7. 量測 C708 與 C848，確認是否符合 1uF ±10%。</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>否 [FAIL]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>END::U1001周邊電路異常::往 U301 查修，確認各腳位電壓、波形，異常則更換U301</t>
+          <t>END::C708/C848 容值異常::更換 C708/C848 後進行其它功能測試</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>皆正常</t>
+          <t>是 [PASS]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NOV_8</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>OCP_8</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NOV_8</t>
+          <t>OCP_8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>F_NOOUTPUT</t>
+          <t>F_OCP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C_NOV_U322GROUP</t>
+          <t>C_OCP_R603R605</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>往 U322 查修：確認 U306、U307、U312 電壓是否正常。</t>
+          <t>8. 量測 R603 右邊電壓是否為 10V、R605 右邊電壓是否為 5V。</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>有異常</t>
+          <t>是 [PASS]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>END::U306/U307/U312其中之一異常::更換異常的該顆IC</t>
+          <t>END::U602 疑似異常::更換 U602 後進行其它功能測試</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>皆無異常</t>
+          <t>否 [FAIL]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>END::往 U319/U320/U321 查修::進一步比對，異常則更換 U319、U320 或 U321</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>OCP_9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OCP_9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>F_OCP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>C_OCP_LAYOUT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>9. 確認 layout 是否斷路：將 10V 的量測點跳線到 C611 上方；5V 的量測點跳線到 R619 下方；Pin5 跳線到 C540。</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>是 [PASS]</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>END::PCB layout 斷路::依上述方式跳線後進行其它功能測試</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>否 [FAIL]</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>OCP_10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OCP_10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>F_OCP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>C_OCP_DGROUP</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>10. 量測 D602/D607/D608，確認是否為 Low(異常)。</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>是 [PASS]</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>END::D602/D607/D608 異常::更換 D602/D607/D608 後進行其它功能測試</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>否 [FAIL]</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>END::保護迴路偵測正常，異常原因未定位::聯繫高階技術支援／原廠技師維修</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/authoring/17108A-5-120_診斷資料.xlsx
+++ b/authoring/17108A-5-120_診斷資料.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="機型" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="異常資訊" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="確認資訊" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="判斷節點" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="機型" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="異常資訊" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認資訊" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="判斷節點" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1073,6 +1073,11 @@
           <t>分類</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>量測位置照片</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1105,6 +1110,11 @@
           <t>保護</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>images/ocp-8.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1137,6 +1147,11 @@
           <t>保護</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>images/ocp-10.png</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1935,6 +1950,11 @@
       <c r="F28" t="inlineStr">
         <is>
           <t>保護</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>images/ocp-9.png</t>
         </is>
       </c>
     </row>
